--- a/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.2.xlsx
+++ b/markets/equipment/dist/20261023_半導體設備市場模型_v0.1.2.xlsx
@@ -7725,7 +7725,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_SK</t>
+      <t xml:space="preserve">20261023_SK</t>
     </r>
     <r>
       <rPr>
@@ -7744,7 +7744,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7915,7 +7915,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_SK</t>
+      <t xml:space="preserve">20261023_SK</t>
     </r>
     <r>
       <rPr>
@@ -7934,7 +7934,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8086,7 +8086,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_SK</t>
+      <t xml:space="preserve">20261023_SK</t>
     </r>
     <r>
       <rPr>
@@ -8105,7 +8105,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8260,7 +8260,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_SK</t>
+      <t xml:space="preserve">20261023_SK</t>
     </r>
     <r>
       <rPr>
@@ -8279,7 +8279,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8436,7 +8436,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -8455,7 +8455,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8701,7 +8701,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -8720,7 +8720,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8985,7 +8985,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -9004,7 +9004,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9231,7 +9231,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -9250,7 +9250,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9345,7 +9345,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -9364,7 +9364,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9629,7 +9629,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -9648,7 +9648,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9856,7 +9856,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -9875,7 +9875,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10064,7 +10064,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20261022_</t>
+      <t xml:space="preserve">20261023_</t>
     </r>
     <r>
       <rPr>
@@ -10083,7 +10083,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
